--- a/campus-tests/SIT Master/Aptitude/set3_medium.xlsx
+++ b/campus-tests/SIT Master/Aptitude/set3_medium.xlsx
@@ -702,32 +702,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 2, 4, 6, 8, ?</t>
+          <t>Find the next number in the series: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -797,27 +797,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 3, 6, 9, 12, 15, 18, ?</t>
+          <t>Find the next number in the series: 3, 7, 13, 21, 31, ?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
